--- a/documents/cuarto/segundo_cuatrimestre/metaheuristicas/trabajo_final/software/cec2017real/code/results_sca/results_cec2017_50.xlsx
+++ b/documents/cuarto/segundo_cuatrimestre/metaheuristicas/trabajo_final/software/cec2017real/code/results_sca/results_cec2017_50.xlsx
@@ -655,7 +655,7 @@
         <v>2742559.9</v>
       </c>
       <c r="V2" t="n">
-        <v>22169735.8</v>
+        <v>23004311.44</v>
       </c>
       <c r="W2" t="n">
         <v>565.40473</v>
@@ -806,7 +806,7 @@
         <v>194710870000</v>
       </c>
       <c r="E4" t="n">
-        <v>6.975718175779999e+80</v>
+        <v>6.97571817578e+80</v>
       </c>
       <c r="F4" t="n">
         <v>469218.71</v>
@@ -1109,7 +1109,7 @@
         <v>142542460000</v>
       </c>
       <c r="E7" t="n">
-        <v>7.272908733392001e+78</v>
+        <v>7.272908733392e+78</v>
       </c>
       <c r="F7" t="n">
         <v>344422.85</v>
@@ -1614,7 +1614,7 @@
         <v>50148718000</v>
       </c>
       <c r="E12" t="n">
-        <v>3.04032331080842e+68</v>
+        <v>3.040323310808421e+68</v>
       </c>
       <c r="F12" t="n">
         <v>146537.63</v>
